--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -508,45 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18.08.2024 12:00</t>
+          <t>16.08.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18 752</t>
+          <t>25 178</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -577,45 +577,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18.08.2024 12:00</t>
+          <t>17.08.2024 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17 924</t>
+          <t>15 220</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -646,45 +646,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18.08.2024 12:00</t>
+          <t>17.08.2024 14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15 220</t>
+          <t>21 029</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -715,45 +715,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.08.2024 12:00</t>
+          <t>17.08.2024 16:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25 178</t>
+          <t>18 523</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,45 +784,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18.08.2024 12:00</t>
+          <t>18.08.2024 10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18 523</t>
+          <t>17 924</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -853,7 +853,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -864,34 +864,34 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20 484</t>
+          <t>18 752</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -922,7 +922,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -933,34 +933,34 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21 029</t>
+          <t>20 484</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -991,7 +991,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1002,34 +1002,34 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Roazhon Park
- (Rennes)</t>
+          <t>Stadium Municipal
+ (Toulouse)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29 778</t>
+          <t>33 150</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1060,45 +1060,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18.08.2024 12:00</t>
+          <t>18.08.2024 15:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Roazhon Park
+ (Rennes)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33 150</t>
+          <t>29 778</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="K10" t="n">

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,459 +508,459 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18.08.2024 12:00</t>
+          <t>16.08.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>25 178</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>551</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>0js8u60b</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>17.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>551</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>jqSiuc6F</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>17.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>551</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>fHYrsJy3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>17.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ripawyyS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>17 924</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2NocJFqd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>Stade Raymond-Kopa
  (Angers)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>18 752</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>SAlF91iL</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Angers</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>IBmris38</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K7" t="n">
         <v>55</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L7" t="n">
         <v>551</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>ripawyyS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>M5VGwpVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>18.08.2024 12:00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>17 924</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>55</v>
-      </c>
-      <c r="L3" t="n">
-        <v>551</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0js8u60b</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>18.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>15 220</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>55</v>
-      </c>
-      <c r="L4" t="n">
-        <v>551</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>SOLVXEbk</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>18.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>25 178</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>551</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>fHYrsJy3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>18.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>18 523</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>M5VGwpVA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>18.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Stade de la Mosson
  (Montpellier)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>20 484</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>551</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jqSiuc6F</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>18.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>21 029</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -991,7 +991,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1002,103 +1002,103 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zkPwWhT1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Roazhon Park
  (Rennes)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>29 778</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>55</v>
-      </c>
-      <c r="L9" t="n">
-        <v>551</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ehlLyFq</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>18.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>33 150</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1121,6 +1121,627 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>42 000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>551</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>551</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,627 +1121,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>38 223</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>50 186</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>59 186</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>67 394</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>35 322</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Allianz Riviera
- (Nice)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>36 178</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Parc des Princes
- (Paris)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>48 229</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>42 000</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>26 109</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,6 +1126,558 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>24.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>24.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>42 000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>25.08.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>551</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.08.2024 12:00</t>
+          <t>25.08.2024 10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Frappart S.
+          <t>Pignard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59 186</t>
+          <t>38 223</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.08.2024 14:00</t>
+          <t>25.08.2024 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kherradji A.
+          <t>Angoula G.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50 186</t>
+          <t>35 322</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.08.2024 16:00</t>
+          <t>25.08.2024 12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Batta F.
+          <t>Dechepy B.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
+          <t>Allianz Riviera
+ (Nice)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>42 000</t>
+          <t>36 178</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -722,6 +722,775 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>25.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>31.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>31.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>25 178</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.08.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pignard J.
- (Fra)</t>
-        </is>
-      </c>
+          <t>30.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38 223</t>
+          <t>59 186</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +577,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Angoula G.
- (Fra)</t>
-        </is>
-      </c>
+          <t>31.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35 322</t>
+          <t>15 220</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +646,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Dechepy B.
- (Fra)</t>
-        </is>
-      </c>
+          <t>31.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Allianz Riviera
- (Nice)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36 178</t>
+          <t>20 484</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +715,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Wattellier E.
- (Fra)</t>
-        </is>
-      </c>
+          <t>31.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
+          <t>Stadium Municipal
+ (Toulouse)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26 109</t>
+          <t>33 150</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +784,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ben El Hadj Salem H.
- (Fra)</t>
-        </is>
-      </c>
+          <t>01.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>67 394</t>
+          <t>18 523</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,45 +853,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30.08.2024 15:45</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59 186</t>
+          <t>18 752</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -947,45 +922,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31.08.2024 12:00</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15 220</t>
+          <t>25 178</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1016,45 +991,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31.08.2024 14:00</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20 484</t>
+          <t>21 029</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1085,45 +1060,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31.08.2024 16:00</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33 150</t>
+          <t>50 186</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1146,351 +1121,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>18 523</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>01.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>18 752</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>01.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>25 178</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>01.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>21 029</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>50 186</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,45 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>31.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Angoula G.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>59 186</t>
+          <t>15 220</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -577,45 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31.08.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>31.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Millot B.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15 220</t>
+          <t>20 484</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -646,45 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.08.2024 14:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>31.08.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Stadium Municipal
+ (Toulouse)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20 484</t>
+          <t>33 150</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -715,45 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.08.2024 16:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>01.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33 150</t>
+          <t>18 523</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,45 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18 523</t>
+          <t>18 752</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -853,7 +878,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -861,37 +886,42 @@
           <t>01.09.2024 12:00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18 752</t>
+          <t>25 178</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -922,7 +952,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -930,37 +960,42 @@
           <t>01.09.2024 12:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Vernice M.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25 178</t>
+          <t>21 029</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -991,45 +1026,50 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>01.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21 029</t>
+          <t>50 186</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1052,75 +1092,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>50 186</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>551</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31.08.2024 12:00</t>
+          <t>01.09.2024 10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Angoula G.
+          <t>Delajod W.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15 220</t>
+          <t>18 523</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31.08.2024 14:00</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Millot B.
+          <t>Stinat J.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20 484</t>
+          <t>18 752</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.08.2024 16:00</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Frappart S.
+          <t>Bollengier M.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33 150</t>
+          <t>25 178</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01.09.2024 10:00</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Delajod W.
+          <t>Vernice M.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18 523</t>
+          <t>21 029</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01.09.2024 12:00</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stinat J.
+          <t>Bastien B.
  (Fra)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18 752</t>
+          <t>50 186</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -870,228 +870,6 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>01.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bollengier M.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>25 178</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>551</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>01.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Vernice M.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>21 029</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>55</v>
-      </c>
-      <c r="L8" t="n">
-        <v>551</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bastien B.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>50 186</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>55</v>
-      </c>
-      <c r="L9" t="n">
-        <v>551</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>vsYzkTIc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
+          <t>13.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18 523</t>
+          <t>42 000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,40 +577,35 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>0dMqm7mA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Stinat J.
- (Fra)</t>
-        </is>
-      </c>
+          <t>14.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Vélodrome
+ (Marseille)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18 752</t>
+          <t>67 394</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -656,50 +646,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CGH7Enso</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bollengier M.
- (Fra)</t>
-        </is>
-      </c>
+          <t>14.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25 178</t>
+          <t>17 924</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +715,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Vernice M.
- (Fra)</t>
-        </is>
-      </c>
+          <t>14.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Parc des Princes
+ (Paris)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21 029</t>
+          <t>48 229</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +784,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bastien B.
- (Fra)</t>
-        </is>
-      </c>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Roazhon Park
+ (Rennes)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50 186</t>
+          <t>29 778</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -870,6 +845,282 @@
         </is>
       </c>
       <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,6 +1126,627 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>21.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>21.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>551</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>551</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,368 +508,1280 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.09.2024 10:00</t>
+          <t>20.09.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>Leonard T.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>551</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>21.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>551</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>21.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>551</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>21.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Pignard J.
  (Fra)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Roazhon Park
- (Rennes)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>29 778</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>22.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Vernice M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Batta F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>27.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>17 924</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>27.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>d2nnj1IE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Rennes</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>28.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>28.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>25 178</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>28.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>Eyf00syR</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Montpellier</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K15" t="n">
         <v>55</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L15" t="n">
         <v>551</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>15.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>29.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>29.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Stade de la Beaujoire
  (Nantes)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>35 322</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>55</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L18" t="n">
         <v>551</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>15.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ben El Hadj Salem H.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>29.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Stade de la Meinau
  (Strasbourg)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>26 109</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>55</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L19" t="n">
         <v>551</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>15.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Wattellier E.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>33 150</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>551</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>15.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dechepy B.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>38 223</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0K4Ww3Ad</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.09.2024 15:45</t>
+          <t>21.09.2024 12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Leonard T.
+          <t>Brisard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Allianz Riviera
- (Nice)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36 178</t>
+          <t>50 186</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,45 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fiy8wfGD</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>21.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Roazhon Park
+ (Rennes)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50 186</t>
+          <t>29 778</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -651,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>noOg1c8K</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21.09.2024 14:00</t>
+          <t>21.09.2024 16:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stinat J.
+          <t>Pignard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Roazhon Park
- (Rennes)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29 778</t>
+          <t>21 029</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -725,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v39B1623</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.09.2024 16:00</t>
+          <t>22.09.2024 10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pignard J.
+          <t>Frappart S.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21 029</t>
+          <t>18 523</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -799,50 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
+          <t>6HPisxHl</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22.09.2024 10:00</t>
+          <t>22.09.2024 12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Frappart S.
+          <t>Vernice M.
  (Fra)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18 523</t>
+          <t>18 752</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -873,7 +878,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -883,40 +888,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vernice M.
+          <t>Batta F.
  (Fra)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18 752</t>
+          <t>15 220</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -947,7 +952,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -957,40 +962,40 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Batta F.
+          <t>Ben El Hadj Salem H.
  (Fra)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15 220</t>
+          <t>20 484</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1021,50 +1026,50 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22.09.2024 12:00</t>
+          <t>22.09.2024 15:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ben El Hadj Salem H.
+          <t>Bastien B.
  (Fra)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20 484</t>
+          <t>59 186</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1087,701 +1092,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>22.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bastien B.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>59 186</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>551</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>27.09.2024 14:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>17 924</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>27.09.2024 16:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Parc des Princes
- (Paris)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>48 229</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>28.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>38 223</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>28.09.2024 14:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>25 178</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>28.09.2024 16:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>18 523</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>29.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>33 150</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>29.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>18 752</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>29.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>35 322</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>29.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>26 109</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,368 +508,1240 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pignard J.
- (Fra)</t>
-        </is>
-      </c>
+          <t>27.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>17 924</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>551</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>27.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>551</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>28.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>551</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade Océane
+ (Le Havre)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25 178</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>28.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>29.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>29.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>29.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>04.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>05.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>42 000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>05.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>05.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Roazhon Park
  (Rennes)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>29 778</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>d2nnj1IE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Rennes</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Eyf00syR</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Montpellier</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K17" t="n">
         <v>55</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L17" t="n">
         <v>551</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>15.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>35 322</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>55</v>
-      </c>
-      <c r="L3" t="n">
-        <v>551</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>15.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ben El Hadj Salem H.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Stade de la Meinau
  (Strasbourg)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>26 109</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>55</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L18" t="n">
         <v>551</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>15.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Wattellier E.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>33 150</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>06.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>55</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L19" t="n">
         <v>551</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>15.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dechepy B.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>38 223</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,12 @@
           <t>27.09.2024 14:00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Stade de l'Abbé-Deschamps
@@ -585,7 +590,12 @@
           <t>27.09.2024 16:00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Parc des Princes
@@ -654,7 +664,12 @@
           <t>28.09.2024 12:00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Letexier F.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Stade Bollaert-Delelis
@@ -723,7 +738,12 @@
           <t>28.09.2024 14:00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dechepy B.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Stade Océane
@@ -792,7 +812,12 @@
           <t>28.09.2024 16:00</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Stade Louis II
@@ -861,7 +886,12 @@
           <t>29.09.2024 10:00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Angoula G.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Stadium Municipal
@@ -930,7 +960,12 @@
           <t>29.09.2024 12:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wattellier E.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Stade Raymond-Kopa
@@ -999,7 +1034,12 @@
           <t>29.09.2024 12:00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kherradji A.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Stade de la Beaujoire
@@ -1068,7 +1108,12 @@
           <t>29.09.2024 15:45</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Delajod W.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Stade de la Meinau
@@ -1121,627 +1166,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>04.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>67 394</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>05.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>42 000</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>05.10.2024 14:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>50 186</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>05.10.2024 16:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Roazhon Park
- (Rennes)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>29 778</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>06.10.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>59 186</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>06.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>15 220</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>06.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>21 029</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>06.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>26 109</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>06.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Allianz Riviera
- (Nice)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>36 178</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27.09.2024 14:00</t>
+          <t>29.09.2024 10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stinat J.
+          <t>Angoula G.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
+          <t>Stadium Municipal
+ (Toulouse)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17 924</t>
+          <t>33 150</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27.09.2024 16:00</t>
+          <t>29.09.2024 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ben El Hadj Salem H.
+          <t>Wattellier E.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Parc des Princes
- (Paris)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48 229</t>
+          <t>18 752</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.09.2024 12:00</t>
+          <t>29.09.2024 12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Letexier F.
+          <t>Kherradji A.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>38 223</t>
+          <t>35 322</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.09.2024 14:00</t>
+          <t>29.09.2024 15:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dechepy B.
+          <t>Delajod W.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25 178</t>
+          <t>26 109</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -796,376 +796,6 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>28.09.2024 16:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bollengier M.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>18 523</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>29.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Angoula G.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>33 150</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L7" t="n">
-        <v>551</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>29.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Wattellier E.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>18 752</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>55</v>
-      </c>
-      <c r="L8" t="n">
-        <v>551</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>29.09.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Kherradji A.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>35 322</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>55</v>
-      </c>
-      <c r="L9" t="n">
-        <v>551</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>29.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>26 109</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>551</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29.09.2024 10:00</t>
+          <t>04.10.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Angoula G.
+          <t>Lissorgue R.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Vélodrome
+ (Marseille)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33 150</t>
+          <t>67 394</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29.09.2024 12:00</t>
+          <t>05.10.2024 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wattellier E.
+          <t>Vernice M.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18 752</t>
+          <t>42 000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.09.2024 12:00</t>
+          <t>05.10.2024 14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kherradji A.
+          <t>Turpin C.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35 322</t>
+          <t>50 186</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,72 +730,511 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.09.2024 15:45</t>
+          <t>05.10.2024 16:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Delajod W.
+          <t>Leonard T.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Millot B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Frappart S.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>Stade de la Meinau
  (Strasbourg)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>26 109</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>nP6UzIU1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Strasbourg</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>55</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L9" t="n">
         <v>551</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brisard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04.10.2024 15:45</t>
+          <t>06.10.2024 10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lissorgue R.
+          <t>Bollengier M.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>67 394</t>
+          <t>59 186</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05.10.2024 12:00</t>
+          <t>06.10.2024 12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vernice M.
+          <t>Millot B.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>42 000</t>
+          <t>15 220</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05.10.2024 14:00</t>
+          <t>06.10.2024 12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turpin C.
+          <t>Bastien B.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50 186</t>
+          <t>21 029</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>tItR6sEf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05.10.2024 16:00</t>
+          <t>06.10.2024 12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leonard T.
+          <t>Frappart S.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Roazhon Park
- (Rennes)</t>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29 778</t>
+          <t>26 109</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06.10.2024 10:00</t>
+          <t>06.10.2024 15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bollengier M.
+          <t>Brisard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
+          <t>Allianz Riviera
+ (Nice)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>59 186</t>
+          <t>36 178</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,50 +878,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Millot B.
- (Fra)</t>
-        </is>
-      </c>
+          <t>18.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Louis II
+ (Monaco)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15 220</t>
+          <t>18 523</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -952,50 +947,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bastien B.
- (Fra)</t>
-        </is>
-      </c>
+          <t>19.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade Auguste-Delaune
- (Reims)</t>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21 029</t>
+          <t>15 220</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tItR6sEf</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1026,40 +1016,35 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Frappart S.
- (Fra)</t>
-        </is>
-      </c>
+          <t>19.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26 109</t>
+          <t>42 000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1100,50 +1085,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brisard J.
- (Fra)</t>
-        </is>
-      </c>
+          <t>19.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Allianz Riviera
- (Nice)</t>
+          <t>Parc des Princes
+ (Paris)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36 178</t>
+          <t>48 229</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1174,45 +1154,45 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18.10.2024 15:45</t>
+          <t>20.10.2024 10:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>18 523</t>
+          <t>25 178</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1235,6 +1215,282 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>17 924</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade de la Beaujoire
+ (Nantes)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>35 322</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,368 +508,1280 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.10.2024 10:00</t>
+          <t>25.10.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kherradji A.
+          <t>Batta F.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Roazhon Park
+ (Rennes)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>29 778</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>CIEe04GT</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>551</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>26.10.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bollengier M.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>18 752</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>55</v>
+      </c>
+      <c r="L3" t="n">
+        <v>551</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brisard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stade Auguste-Delaune
+ (Reims)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>21 029</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>551</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bastien B.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>551</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Stinat J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>59 186</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>551</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>27.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20 484</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>551</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>27.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Pignard J.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Allianz Riviera
+ (Nice)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>36 178</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>551</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>27.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ben El Hadj Salem H.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>26 109</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>veuetnGG</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nantes</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>55</v>
+      </c>
+      <c r="L9" t="n">
+        <v>551</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>27.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Letexier F.
+ (Fra)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stade Vélodrome
+ (Marseille)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>67 394</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>55</v>
+      </c>
+      <c r="L10" t="n">
+        <v>551</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01.11.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SAlF91iL</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01.11.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stade Pierre-Mauroy
+ (Villeneuve d'Ascq)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>50 186</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pfDZL71o</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2akflumR</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>02.11.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>02.11.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Francis-Le Blé
+ (Brest)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>15 220</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>YagoQJpq</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>02.11.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>42 000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>nP6UzIU1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>03.11.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stadium Municipal
+ (Toulouse)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>33 150</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>tItR6sEf</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Reims</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>55</v>
+      </c>
+      <c r="L16" t="n">
+        <v>551</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>03.11.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stade de l'Abbé-Deschamps
+ (Auxerre)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>17 924</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>MTLr36WA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>d2nnj1IE</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>55</v>
+      </c>
+      <c r="L17" t="n">
+        <v>551</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>03.11.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Stade Océane
  (Le Havre)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>25 178</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>CIEe04GT</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Le Havre</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>55</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L18" t="n">
         <v>551</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>20.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Batta F.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>17 924</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>55</v>
-      </c>
-      <c r="L3" t="n">
-        <v>551</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>20.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Angoula G.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>03.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Stade de la Beaujoire
  (Nantes)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>35 322</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>veuetnGG</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Nantes</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>55</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L19" t="n">
         <v>551</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>france</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>20.10.2024 12:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Delajod W.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>33 150</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>551</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>20.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Turpin C.
- (Fra)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20 484</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>55</v>
-      </c>
-      <c r="L6" t="n">
-        <v>551</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,7 +886,12 @@
           <t>27.10.2024 13:00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Leonard T.
+ (Fra)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Stade de la Mosson
@@ -1161,627 +1166,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01.11.2024 15:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Louis II
- (Monaco)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>18 523</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>01.11.2024 17:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>50 186</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>02.11.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Parc des Princes
- (Paris)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>48 229</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>02.11.2024 15:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>15 220</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>02.11.2024 17:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>42 000</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>03.11.2024 11:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>33 150</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>03.11.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>17 924</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>03.11.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>25 178</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>03.11.2024 16:45</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>35 322</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,627 +1166,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Gp6AbAAT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>08.11.2024 16:45</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stade Vélodrome
- (Marseille)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>67 394</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SblU3Hee</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Marseille</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MTLr36WA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Auxerre</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>55</v>
-      </c>
-      <c r="L11" t="n">
-        <v>551</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>09.11.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stade de la Meinau
- (Strasbourg)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>26 109</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>nP6UzIU1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Strasbourg</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2PIvr8o4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>551</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bJl87mmp</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>09.11.2024 15:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stade Bollaert-Delelis
- (Lens)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>38 223</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>IBmris38</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Lens</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>veuetnGG</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>55</v>
-      </c>
-      <c r="L13" t="n">
-        <v>551</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>09.11.2024 17:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stade Raymond-Kopa
- (Angers)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>18 752</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>SAlF91iL</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Angers</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>CjhkPw0k</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>55</v>
-      </c>
-      <c r="L14" t="n">
-        <v>551</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>10.11.2024 11:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Allianz Riviera
- (Nice)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>36 178</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>YagoQJpq</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pfDZL71o</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Lille</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>10.11.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Stade Océane
- (Le Havre)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>25 178</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CIEe04GT</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Le Havre</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>tItR6sEf</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Reims</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>55</v>
-      </c>
-      <c r="L16" t="n">
-        <v>551</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10.11.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stade de la Mosson
- (Montpellier)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>20 484</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Eyf00syR</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Montpellier</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Cr4VGaUl</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Brest</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>55</v>
-      </c>
-      <c r="L17" t="n">
-        <v>551</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>10.11.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Roazhon Park
- (Rennes)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>29 778</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>d2nnj1IE</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Rennes</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>MLmY2yB1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>55</v>
-      </c>
-      <c r="L18" t="n">
-        <v>551</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>10.11.2024 16:45</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Parc Olympique Lyonnais
- (Lyon)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>59 186</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2akflumR</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>YL2QybFe</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>St Etienne</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>551</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.11.2024 15:00</t>
+          <t>08.11.2024 16:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kherradji A.
+          <t>Bollengier M.
  (Fra)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stade Louis II
- (Monaco)</t>
+          <t>Stade Vélodrome
+ (Marseille)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18 523</t>
+          <t>67 394</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2PIvr8o4</t>
+          <t>SblU3Hee</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SAlF91iL</t>
+          <t>MTLr36WA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Angers</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01.11.2024 17:00</t>
+          <t>09.11.2024 13:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brisard J.
+          <t>Dechepy B.
  (Fra)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stade Pierre-Mauroy
- (Villeneuve d'Ascq)</t>
+          <t>Stade de la Meinau
+ (Strasbourg)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50 186</t>
+          <t>26 109</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pfDZL71o</t>
+          <t>nP6UzIU1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2akflumR</t>
+          <t>2PIvr8o4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>02.11.2024 13:00</t>
+          <t>09.11.2024 15:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Delajod W.
+          <t>Turpin C.
  (Fra)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Parc des Princes
- (Paris)</t>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>48 229</t>
+          <t>38 223</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CjhkPw0k</t>
+          <t>IBmris38</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IBmris38</t>
+          <t>veuetnGG</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>02.11.2024 15:00</t>
+          <t>09.11.2024 17:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turpin C.
+          <t>Millot B.
  (Fra)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stade Francis-Le Blé
- (Brest)</t>
+          <t>Stade Raymond-Kopa
+ (Angers)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15 220</t>
+          <t>18 752</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cr4VGaUl</t>
+          <t>SAlF91iL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Angers</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>YagoQJpq</t>
+          <t>CjhkPw0k</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>02.11.2024 17:00</t>
+          <t>10.11.2024 11:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wattellier E.
+          <t>Stinat J.
  (Fra)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stade Geoffroy-Guichard
- (Saint-Étienne)</t>
+          <t>Allianz Riviera
+ (Nice)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42 000</t>
+          <t>36 178</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>YL2QybFe</t>
+          <t>YagoQJpq</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>St Etienne</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>nP6UzIU1</t>
+          <t>pfDZL71o</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,40 +878,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>03.11.2024 11:00</t>
+          <t>10.11.2024 13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vernice M.
+          <t>Ben El Hadj Salem H.
  (Fra)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadium Municipal
- (Toulouse)</t>
+          <t>Stade Océane
+ (Le Havre)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33 150</t>
+          <t>25 178</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MLmY2yB1</t>
+          <t>CIEe04GT</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -952,50 +952,50 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>03.11.2024 13:00</t>
+          <t>10.11.2024 13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Angoula G.
+          <t>Pignard J.
  (Fra)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stade de l'Abbé-Deschamps
- (Auxerre)</t>
+          <t>Stade de la Mosson
+ (Montpellier)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17 924</t>
+          <t>20 484</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MTLr36WA</t>
+          <t>Eyf00syR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>d2nnj1IE</t>
+          <t>Cr4VGaUl</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1026,50 +1026,50 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>03.11.2024 13:00</t>
+          <t>10.11.2024 13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frappart S.
+          <t>Lissorgue R.
  (Fra)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stade Océane
- (Le Havre)</t>
+          <t>Roazhon Park
+ (Rennes)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25 178</t>
+          <t>29 778</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CIEe04GT</t>
+          <t>d2nnj1IE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Eyf00syR</t>
+          <t>MLmY2yB1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1100,50 +1100,50 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>03.11.2024 16:45</t>
+          <t>10.11.2024 16:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dechepy B.
+          <t>Delajod W.
  (Fra)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stade de la Beaujoire
- (Nantes)</t>
+          <t>Parc Olympique Lyonnais
+ (Lyon)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35 322</t>
+          <t>59 186</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>veuetnGG</t>
+          <t>2akflumR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SblU3Hee</t>
+          <t>YL2QybFe</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>St Etienne</t>
         </is>
       </c>
       <c r="K10" t="n">

--- a/data/france/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,6 +1166,282 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22.11.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stade Louis II
+ (Monaco)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>18 523</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2PIvr8o4</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Cr4VGaUl</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>551</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>22.11.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Parc des Princes
+ (Paris)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>48 229</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CjhkPw0k</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MLmY2yB1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L12" t="n">
+        <v>551</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>23.11.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stade Bollaert-Delelis
+ (Lens)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>38 223</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>IBmris38</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SblU3Hee</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>551</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>23.11.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stade Geoffroy-Guichard
+ (Saint-Étienne)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>42 000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>YL2QybFe</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>St Etienne</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Eyf00syR</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Montpellier</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="n">
+        <v>551</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
